--- a/artfynd/A 56624-2022 artfynd.xlsx
+++ b/artfynd/A 56624-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56624-2022 artfynd.xlsx
+++ b/artfynd/A 56624-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>81745564</v>
       </c>
       <c r="B2" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>389207.9128997151</v>
+        <v>389208</v>
       </c>
       <c r="R2" t="n">
-        <v>6651414.241032528</v>
+        <v>6651414</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,19 +753,9 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-10-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 56624-2022 artfynd.xlsx
+++ b/artfynd/A 56624-2022 artfynd.xlsx
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81745564</v>
+        <v>81745408</v>
       </c>
       <c r="B2" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gåstjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>389208</v>
+        <v>389209</v>
       </c>
       <c r="R2" t="n">
-        <v>6651414</v>
+        <v>6651408</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81745408</v>
+        <v>81745564</v>
       </c>
       <c r="B3" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gåstjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>389209.2360795157</v>
+        <v>389208</v>
       </c>
       <c r="R3" t="n">
-        <v>6651408.19240658</v>
+        <v>6651414</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,19 +845,9 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-10-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
